--- a/src/database/client_data_result.xlsx
+++ b/src/database/client_data_result.xlsx
@@ -541,16 +541,20 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>1149649258000</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1149649258000</t>
+        </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>NPI-1</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>1189183146000</v>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1189183146000</t>
+        </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -645,16 +649,20 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>1151609207000</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>1151609207000</t>
+        </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>NPI-1</t>
         </is>
       </c>
-      <c r="C3" t="n">
-        <v>1760751880000</v>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1760751880000</t>
+        </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -745,25 +753,29 @@
       <c r="V3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>1159924781000</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1151493808000</t>
+        </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
           <t>NPI-1</t>
         </is>
       </c>
-      <c r="C4" t="n">
-        <v>1701206940000</v>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1210105909000</t>
+        </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1306931894</t>
+          <t>1427085877</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>[{'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'MAILING', 'address_type': 'DOM', 'address_1': '3260 HOSPITAL DR', 'city': 'JUNEAU', 'state': 'AK', 'postal_code': '998017808', 'telephone_number': '907-796-8631', 'fax_number': '907-796-8455'}, {'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'LOCATION', 'address_type': 'DOM', 'address_1': '3260 HOSPITAL DR', 'city': 'JUNEAU', 'state': 'AK', 'postal_code': '998017808', 'telephone_number': '907-796-8631', 'fax_number': '907-796-8455'}]</t>
+          <t>[{'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'MAILING', 'address_type': 'DOM', 'address_1': '1120 HUFFMAN RD # 587', 'city': 'ANCHORAGE', 'state': 'AK', 'postal_code': '995153516', 'telephone_number': '907-277-1111', 'fax_number': '907-277-1136'}, {'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'LOCATION', 'address_type': 'DOM', 'address_1': '2841 DEBARR RD', 'address_2': 'STE 46', 'city': 'ANCHORAGE', 'state': 'AK', 'postal_code': '995082932', 'telephone_number': '907-277-1111', 'fax_number': '907-277-1136'}]</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -773,12 +785,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>[{'code': '207X00000X', 'taxonomy_group': '', 'desc': 'Orthopaedic Surgery', 'state': 'AK', 'license': '5104', 'primary': True}]</t>
+          <t>[{'code': '208600000X', 'taxonomy_group': '', 'desc': 'Surgery', 'state': 'AK', 'license': '4943', 'primary': True}]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>[{'code': '05', 'desc': 'MEDICAID', 'issuer': None, 'identifier': 'MD6070', 'state': 'AK'}]</t>
+          <t>[{'code': '05', 'desc': 'MEDICAID', 'issuer': None, 'identifier': 'MD49431', 'state': 'AK'}]</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -793,17 +805,17 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>TED</t>
+          <t>GRANT</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>SCHWARTING</t>
+          <t>SEARLES</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>LEWIS</t>
+          <t>M</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -813,7 +825,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -823,47 +835,55 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2006-10-03</t>
+          <t>2006-06-28</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2023-11-28</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>2023-11-28</t>
-        </is>
-      </c>
+          <t>2008-05-06</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Dr.</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>1151493808000</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1159924781000</t>
+        </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
           <t>NPI-1</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v>1210105909000</v>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1701206940000</t>
+        </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1427085877</t>
+          <t>1306931894</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>[{'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'MAILING', 'address_type': 'DOM', 'address_1': '1120 HUFFMAN RD # 587', 'city': 'ANCHORAGE', 'state': 'AK', 'postal_code': '995153516', 'telephone_number': '907-277-1111', 'fax_number': '907-277-1136'}, {'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'LOCATION', 'address_type': 'DOM', 'address_1': '2841 DEBARR RD', 'address_2': 'STE 46', 'city': 'ANCHORAGE', 'state': 'AK', 'postal_code': '995082932', 'telephone_number': '907-277-1111', 'fax_number': '907-277-1136'}]</t>
+          <t>[{'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'MAILING', 'address_type': 'DOM', 'address_1': '3260 HOSPITAL DR', 'city': 'JUNEAU', 'state': 'AK', 'postal_code': '998017808', 'telephone_number': '907-796-8631', 'fax_number': '907-796-8455'}, {'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'LOCATION', 'address_type': 'DOM', 'address_1': '3260 HOSPITAL DR', 'city': 'JUNEAU', 'state': 'AK', 'postal_code': '998017808', 'telephone_number': '907-796-8631', 'fax_number': '907-796-8455'}]</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -873,12 +893,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>[{'code': '208600000X', 'taxonomy_group': '', 'desc': 'Surgery', 'state': 'AK', 'license': '4943', 'primary': True}]</t>
+          <t>[{'code': '207X00000X', 'taxonomy_group': '', 'desc': 'Orthopaedic Surgery', 'state': 'AK', 'license': '5104', 'primary': True}]</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>[{'code': '05', 'desc': 'MEDICAID', 'issuer': None, 'identifier': 'MD49431', 'state': 'AK'}]</t>
+          <t>[{'code': '05', 'desc': 'MEDICAID', 'issuer': None, 'identifier': 'MD6070', 'state': 'AK'}]</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -893,65 +913,61 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>GRANT</t>
+          <t>TED</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>SEARLES</t>
+          <t>SCHWARTING</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
+          <t>LEWIS</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
           <t>M</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>MD</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2006-06-28</t>
+          <t>2006-10-03</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2008-05-06</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr"/>
+          <t>2023-11-28</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>2023-11-28</t>
+        </is>
+      </c>
       <c r="T5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Dr.</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1151443437000</t>
+          <t>1160693270000</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -961,17 +977,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1462897761000</t>
+          <t>1183947785000</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1144257882</t>
+          <t>1497844617</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>[{'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'MAILING', 'address_type': 'DOM', 'address_1': '701 N UNIVERSITY AVE', 'address_2': 'SUITE 203', 'city': 'LITTLE ROCK', 'state': 'AR', 'postal_code': '722052936', 'telephone_number': '501-664-2434', 'fax_number': '501-907-7768'}, {'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'LOCATION', 'address_type': 'DOM', 'address_1': '701 N UNIVERSITY AVE', 'address_2': 'SUITE 203', 'city': 'LITTLE ROCK', 'state': 'AR', 'postal_code': '722052936', 'telephone_number': '501-664-2434', 'fax_number': '501-907-7768'}]</t>
+          <t>[{'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'MAILING', 'address_type': 'DOM', 'address_1': '3268 HOSPITAL DR', 'city': 'JUNEAU', 'state': 'AK', 'postal_code': '998017808', 'telephone_number': '907-586-4126', 'fax_number': '907-586-4134'}, {'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'LOCATION', 'address_type': 'DOM', 'address_1': '3268 HOSPITAL DR', 'city': 'JUNEAU', 'state': 'AK', 'postal_code': '998017808', 'telephone_number': '907-586-4126', 'fax_number': '907-586-4134'}]</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -981,12 +997,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>[{'code': '208C00000X', 'taxonomy_group': '', 'desc': 'Colon &amp; Rectal Surgery', 'state': 'AR', 'license': 'C-6895', 'primary': True}]</t>
+          <t>[{'code': '174400000X', 'taxonomy_group': '', 'desc': 'Specialist', 'state': 'AK', 'license': '282764', 'primary': True}]</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>[{'code': '05', 'desc': 'MEDICAID', 'issuer': None, 'identifier': '111689001', 'state': 'AR'}]</t>
+          <t>[{'code': '05', 'desc': 'MEDICAID', 'issuer': None, 'identifier': 'MD3105', 'state': 'AK'}]</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1001,17 +1017,17 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>KURTIS</t>
+          <t>DAVID</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>VINSANT</t>
+          <t>MILLER</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>S.</t>
+          <t>ALLEN</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1021,7 +1037,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1031,12 +1047,12 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2006-06-27</t>
+          <t>2006-10-12</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2016-05-10</t>
+          <t>2007-07-08</t>
         </is>
       </c>
       <c r="S6" t="inlineStr"/>
@@ -1047,7 +1063,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>Dr.</t>
+          <t>--</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1171,7 +1187,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1160693270000</t>
+          <t>1151443437000</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1181,17 +1197,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1183947785000</t>
+          <t>1462897761000</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1497844617</t>
+          <t>1144257882</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>[{'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'MAILING', 'address_type': 'DOM', 'address_1': '3268 HOSPITAL DR', 'city': 'JUNEAU', 'state': 'AK', 'postal_code': '998017808', 'telephone_number': '907-586-4126', 'fax_number': '907-586-4134'}, {'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'LOCATION', 'address_type': 'DOM', 'address_1': '3268 HOSPITAL DR', 'city': 'JUNEAU', 'state': 'AK', 'postal_code': '998017808', 'telephone_number': '907-586-4126', 'fax_number': '907-586-4134'}]</t>
+          <t>[{'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'MAILING', 'address_type': 'DOM', 'address_1': '701 N UNIVERSITY AVE', 'address_2': 'SUITE 203', 'city': 'LITTLE ROCK', 'state': 'AR', 'postal_code': '722052936', 'telephone_number': '501-664-2434', 'fax_number': '501-907-7768'}, {'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'LOCATION', 'address_type': 'DOM', 'address_1': '701 N UNIVERSITY AVE', 'address_2': 'SUITE 203', 'city': 'LITTLE ROCK', 'state': 'AR', 'postal_code': '722052936', 'telephone_number': '501-664-2434', 'fax_number': '501-907-7768'}]</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1201,12 +1217,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>[{'code': '174400000X', 'taxonomy_group': '', 'desc': 'Specialist', 'state': 'AK', 'license': '282764', 'primary': True}]</t>
+          <t>[{'code': '208C00000X', 'taxonomy_group': '', 'desc': 'Colon &amp; Rectal Surgery', 'state': 'AR', 'license': 'C-6895', 'primary': True}]</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>[{'code': '05', 'desc': 'MEDICAID', 'issuer': None, 'identifier': 'MD3105', 'state': 'AK'}]</t>
+          <t>[{'code': '05', 'desc': 'MEDICAID', 'issuer': None, 'identifier': '111689001', 'state': 'AR'}]</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1221,17 +1237,17 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>DAVID</t>
+          <t>KURTIS</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>MILLER</t>
+          <t>VINSANT</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>ALLEN</t>
+          <t>S.</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1241,7 +1257,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1251,12 +1267,12 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2006-10-12</t>
+          <t>2006-06-27</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2007-07-08</t>
+          <t>2016-05-10</t>
         </is>
       </c>
       <c r="S8" t="inlineStr"/>
@@ -1267,7 +1283,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>Dr.</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
